--- a/AfterToken/Configs/GameConfig/Datas/portal.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/portal.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,7 +623,7 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>1002</v>
+        <v>1101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Press E to go to next level</t>
+          <t>Press E to go to Stage 102</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -657,32 +657,27 @@
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>1003</v>
+        <v>1102</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>portal_custom_scene</t>
+          <t>portal_next_level</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>BattleScene_L02</t>
-        </is>
+        <v>103</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>all_enemies_defeated</t>
         </is>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Press E to go to Stage 2</t>
+          <t>Press E to go to Stage 103</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -696,21 +691,16 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>1004</v>
+        <v>2001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>portal_custom_scene</t>
+          <t>portal_select_level</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>BattleScene_L03</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>none</t>
@@ -721,7 +711,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Press E to go to Stage 3</t>
+          <t>Press E to deploy</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -730,110 +720,6 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="n">
-        <v>1101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>portal_next_level</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>102</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>all_enemies_defeated</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Press E to go to Stage 102</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fade_to_gray</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="n">
-        <v>1102</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>portal_next_level</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>103</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>all_enemies_defeated</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Press E to go to Stage 103</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fade_to_gray</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="n">
-        <v>2001</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>portal_select_level</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Press E to deploy</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fade_to_gray</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
         <v>0.5</v>
       </c>
     </row>
